--- a/examples/HO_SO_CAU_KM19_529/04_CO_GIOI_THIET_BI_VA_DAU_DIEZEL/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/04_CO_GIOI_THIET_BI_VA_DAU_DIEZEL/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -150,8 +150,31 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="005A3718"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -212,8 +235,14 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE2D3"/>
+        <bgColor rgb="00EFE2D3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -249,11 +278,26 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -389,6 +433,25 @@
     <xf numFmtId="4" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="26" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19261,16 +19324,6 @@
           <t>BẢNG TỔNG HỢP CA MÁY &amp; PHƯƠNG TIỆN HUY ĐỘNG THEO NGÀY (CÔNG TRƯỜNG CẦU KM19)</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="34" t="n"/>
-      <c r="G39" s="34" t="n"/>
-      <c r="H39" s="34" t="n"/>
-      <c r="I39" s="33" t="n"/>
-      <c r="J39" s="33" t="n"/>
-      <c r="K39" s="33" t="n"/>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="35" t="n"/>
       <c r="N39" s="33" t="n"/>
       <c r="O39" s="36" t="n"/>
     </row>
@@ -40195,430 +40248,640 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BẢNG ĐỐI CHIẾU KHỐI LƯỢNG THỰC TẾ HỒ SƠ THIẾT KẾ CẦU KM19+529.080</t>
+      <c r="A1" s="67" t="inlineStr">
+        <is>
+          <t>BẢNG ĐỐI CHIẾU KHỐI LƯỢNG THIẾT KẾ CẦU KM19+529.080 (CHUẨN HÓA TÁCH BẠCH TRỤ T1 &amp; T2)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Hạng mục kết cấu Cầu Km19+529.080</t>
         </is>
       </c>
-      <c r="C3" s="56" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>Quy cách / Kích thước</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>Khối lượng Bê tông (m3)</t>
         </is>
       </c>
-      <c r="E3" s="56" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>Mác Bê tông</t>
         </is>
       </c>
-      <c r="F3" s="56" t="inlineStr">
+      <c r="F3" s="68" t="inlineStr">
         <is>
           <t>Ván khuôn tiếp xúc (m2)</t>
         </is>
       </c>
-      <c r="G3" s="56" t="inlineStr">
+      <c r="G3" s="68" t="inlineStr">
         <is>
           <t>Cốt thép thường (tấn)</t>
         </is>
       </c>
-      <c r="H3" s="56" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>Cáp DƯL / Ghi chú kỹ thuật</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="A4" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>26 Cọc khoan nhồi D1200mm (M1, M2, T1, T2)</t>
         </is>
       </c>
-      <c r="C4" s="57" t="inlineStr">
-        <is>
-          <t>26 cọc, L_tb=33.5m</t>
-        </is>
-      </c>
-      <c r="D4" s="59" t="n">
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>26 cọc, L_tb=33.5m, ngàm đá Karst</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="n">
         <v>1006.54</v>
       </c>
-      <c r="E4" s="57" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="F4" s="59" t="n">
+      <c r="F4" s="71" t="n">
         <v>3286</v>
       </c>
-      <c r="G4" s="65" t="n">
+      <c r="G4" s="71" t="n">
         <v>116.35</v>
       </c>
-      <c r="H4" s="58" t="inlineStr">
-        <is>
-          <t>Bao gồm cả BT đập đầu cọc nhô lên 1.0m</t>
+      <c r="H4" s="70" t="inlineStr">
+        <is>
+          <t>Khoan ngàm đá hang Karst sâu 5m</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="n">
+      <c r="A5" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Bê tông lót đáy bệ móng mố M1, M2 &amp; trụ T1, T2</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
-        <is>
-          <t>Dày 10cm đá 1x2</t>
-        </is>
-      </c>
-      <c r="D5" s="59" t="n">
+      <c r="C5" s="70" t="inlineStr">
+        <is>
+          <t>Dày 10cm đá 1x2 đáy bệ móng</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="n">
         <v>42.15</v>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="F5" s="59" t="n">
+      <c r="F5" s="71" t="n">
         <v>84.3</v>
       </c>
-      <c r="G5" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="58" t="inlineStr">
-        <is>
-          <t>Đổ lót đáy móng sau đào đất đá</t>
+      <c r="G5" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="70" t="inlineStr">
+        <is>
+          <t>Đổ lót đáy móng sau đào đá</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="n">
+      <c r="A6" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="58" t="inlineStr">
-        <is>
-          <t>Bệ móng mố M1, M2 &amp; bệ trụ T1, T2</t>
-        </is>
-      </c>
-      <c r="C6" s="57" t="inlineStr">
-        <is>
-          <t>Bệ M1,M2,T1,T2</t>
-        </is>
-      </c>
-      <c r="D6" s="59" t="n">
-        <v>517.48</v>
-      </c>
-      <c r="E6" s="57" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
+        <is>
+          <t>Bệ móng mố M1 (78.4 m3) &amp; mố M2 (94.8 m3)</t>
+        </is>
+      </c>
+      <c r="C6" s="70" t="inlineStr">
+        <is>
+          <t>Bệ móng chữ nhật ngàm cọc</t>
+        </is>
+      </c>
+      <c r="D6" s="71" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="F6" s="59" t="n">
-        <v>586.2</v>
-      </c>
-      <c r="G6" s="65" t="n">
-        <v>85.42</v>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
-        <is>
-          <t>Cốt thép chịu uốn chính Phi 32</t>
+      <c r="F6" s="71" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H6" s="70" t="inlineStr">
+        <is>
+          <t>Cốt thép chịu lực Phi 28 - Phi 32</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="n">
+      <c r="A7" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="58" t="inlineStr">
-        <is>
-          <t>Thân trụ đặc T1 (H=14.5m) &amp; T2 (H=11.4m)</t>
-        </is>
-      </c>
-      <c r="C7" s="57" t="inlineStr">
-        <is>
-          <t>Trụ thân đặc vát</t>
-        </is>
-      </c>
-      <c r="D7" s="59" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="E7" s="57" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>Bệ móng trụ T1 (11.6m x 8.0m x 2.0m)</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>Khối hộp 11.6x8.0x2.0m KHÔNG VÁT</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="n">
+        <v>184.243</v>
+      </c>
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="F7" s="59" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="G7" s="65" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="H7" s="58" t="inlineStr">
-        <is>
-          <t>Đà giáo leo thi công 3 đợt</t>
+      <c r="F7" s="71" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="H7" s="70" t="inlineStr">
+        <is>
+          <t>Chuẩn hóa Zero-vát bệ T1 (184.243 m3)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="n">
+      <c r="A8" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="58" t="inlineStr">
-        <is>
-          <t>Thân mố chân dê M1 &amp; mố chữ U M2</t>
-        </is>
-      </c>
-      <c r="C8" s="57" t="inlineStr">
-        <is>
-          <t>Mố tường đặc &amp; tai mố</t>
-        </is>
-      </c>
-      <c r="D8" s="59" t="n">
-        <v>138.4</v>
-      </c>
-      <c r="E8" s="57" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>Bệ móng trụ T2 (11.6m x 8.0m x 2.0m)</t>
+        </is>
+      </c>
+      <c r="C8" s="70" t="inlineStr">
+        <is>
+          <t>Khối hộp 11.6x8.0x2.0m KHÔNG VÁT</t>
+        </is>
+      </c>
+      <c r="D8" s="71" t="n">
+        <v>184.243</v>
+      </c>
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="F8" s="59" t="n">
-        <v>356.8</v>
-      </c>
-      <c r="G8" s="65" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="H8" s="58" t="inlineStr">
-        <is>
-          <t>Bao gồm tường thân, tường cánh, đá kê</t>
+      <c r="F8" s="71" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="H8" s="70" t="inlineStr">
+        <is>
+          <t>Chuẩn hóa Zero-vát bệ T2 (184.243 m3)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="n">
+      <c r="A9" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="58" t="inlineStr">
-        <is>
-          <t>Xà mũ trụ T1, T2 &amp; ụ chống xô</t>
-        </is>
-      </c>
-      <c r="C9" s="57" t="inlineStr">
-        <is>
-          <t>Xà mũ vát đầu trụ</t>
-        </is>
-      </c>
-      <c r="D9" s="59" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="E9" s="57" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>Thân mố chân dê M1 (68.2 m3) &amp; mố chữ U M2 (70.2 m3)</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>Mố tường đặc kèm tường cánh</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="F9" s="59" t="n">
-        <v>228.4</v>
-      </c>
-      <c r="G9" s="65" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="H9" s="58" t="inlineStr">
-        <is>
-          <t>Lắp đặt đá kê gối cầu sai số &lt;=2mm</t>
+      <c r="F9" s="71" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="H9" s="70" t="inlineStr">
+        <is>
+          <t>Bao gồm tường thân, tường cánh, đá kê</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="n">
+      <c r="A10" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="58" t="inlineStr">
-        <is>
-          <t>15 Phiến dầm Super-T L=38.2m tại bãi đúc</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="inlineStr">
-        <is>
-          <t>15 phiến dầm định hình</t>
-        </is>
-      </c>
-      <c r="D10" s="59" t="n">
-        <v>434.8</v>
-      </c>
-      <c r="E10" s="57" t="inlineStr">
-        <is>
-          <t>C45/55</t>
-        </is>
-      </c>
-      <c r="F10" s="59" t="n">
-        <v>2610</v>
-      </c>
-      <c r="G10" s="65" t="n">
-        <v>96.72</v>
-      </c>
-      <c r="H10" s="58" t="inlineStr">
-        <is>
-          <t>27.78 tấn cáp DƯL 15.2mm (660 tao)</t>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>Thân trụ đặc T1 (H=23.35m, 3 đốt thân có vát)</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>Đốt 3 chân loe, Đốt 2 thân, Đốt 1 đỉnh</t>
+        </is>
+      </c>
+      <c r="D10" s="71" t="n">
+        <v>234.922</v>
+      </c>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="F10" s="71" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H10" s="70" t="inlineStr">
+        <is>
+          <t>Vát góc 4 cạnh, đà giáo leo thi công 3 đợt</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="n">
+      <c r="A11" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="58" t="inlineStr">
-        <is>
-          <t>Dầm ngang mố trụ &amp; bản liên tục nhiệt</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="inlineStr">
-        <is>
-          <t>Bê tông nối nhịp</t>
-        </is>
-      </c>
-      <c r="D11" s="59" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="E11" s="57" t="inlineStr">
-        <is>
-          <t>C35</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="n">
-        <v>185</v>
-      </c>
-      <c r="G11" s="65" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H11" s="58" t="inlineStr">
-        <is>
-          <t>Liên kết đầu dầm Super-T trên đỉnh trụ</t>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>Thân trụ đặc T2 (H=25.45m, 3 đốt thân có vát)</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>Đốt 3 chân loe, Đốt 2 thân, Đốt 1 đỉnh</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="n">
+        <v>266.791</v>
+      </c>
+      <c r="E11" s="69" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="F11" s="71" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H11" s="70" t="inlineStr">
+        <is>
+          <t>Vát góc 4 cạnh, đà giáo leo thi công 3 đợt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="n">
+      <c r="A12" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="58" t="inlineStr">
-        <is>
-          <t>Bản mặt cầu tại chỗ &amp; gờ lan can</t>
-        </is>
-      </c>
-      <c r="C12" s="57" t="inlineStr">
-        <is>
-          <t>Dày 180mm, L=118.2m</t>
-        </is>
-      </c>
-      <c r="D12" s="59" t="n">
-        <v>265.4</v>
-      </c>
-      <c r="E12" s="57" t="inlineStr">
-        <is>
-          <t>C35</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="n">
-        <v>1420</v>
-      </c>
-      <c r="G12" s="65" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="H12" s="58" t="inlineStr">
-        <is>
-          <t>Phối hợp 510 tấm ván khuôn đúc sẵn</t>
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>Xà mũ trụ T1 &amp; khối ụ chống xô</t>
+        </is>
+      </c>
+      <c r="C12" s="70" t="inlineStr">
+        <is>
+          <t>Xà mũ vát đầu trụ T1, L=11.6m</t>
+        </is>
+      </c>
+      <c r="D12" s="71" t="n">
+        <v>128.851</v>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="F12" s="71" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H12" s="70" t="inlineStr">
+        <is>
+          <t>Đá kê gối cầu sai số &lt;= 2mm</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="n">
+      <c r="A13" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="58" t="inlineStr">
-        <is>
-          <t>Bản quá độ sau 2 mố &amp; đắp K98 đầu cầu</t>
-        </is>
-      </c>
-      <c r="C13" s="57" t="inlineStr">
-        <is>
-          <t>2 bản L=5.0m</t>
-        </is>
-      </c>
-      <c r="D13" s="59" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="E13" s="57" t="inlineStr">
-        <is>
-          <t>C25</t>
-        </is>
-      </c>
-      <c r="F13" s="59" t="n">
-        <v>86</v>
-      </c>
-      <c r="G13" s="65" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H13" s="58" t="inlineStr">
-        <is>
-          <t>Đắp chọn lọc K98 đầm chặt</t>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>Xà mũ trụ T2 &amp; khối ụ chống xô</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>Xà mũ vát đầu trụ T2, L=11.6m</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="n">
+        <v>145.026</v>
+      </c>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H13" s="70" t="inlineStr">
+        <is>
+          <t>Đá kê gối cầu sai số &lt;= 2mm</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="n"/>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="A14" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>15 Phiến dầm Super-T L=38.2m tại bãi đúc</t>
+        </is>
+      </c>
+      <c r="C14" s="70" t="inlineStr">
+        <is>
+          <t>15 phiến dầm mặt cắt I loe</t>
+        </is>
+      </c>
+      <c r="D14" s="71" t="n">
+        <v>434.8</v>
+      </c>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>C45/55</t>
+        </is>
+      </c>
+      <c r="F14" s="71" t="n">
+        <v>2610</v>
+      </c>
+      <c r="G14" s="71" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="H14" s="70" t="inlineStr">
+        <is>
+          <t>27.78 tấn cáp DƯL 15.2mm (660 tao)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>Dầm ngang mố trụ &amp; bản liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="C15" s="70" t="inlineStr">
+        <is>
+          <t>Bê tông nối nhịp đỉnh trụ</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="F15" s="71" t="n">
+        <v>185</v>
+      </c>
+      <c r="G15" s="71" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H15" s="70" t="inlineStr">
+        <is>
+          <t>Liên kết dầm Super-T trên đỉnh mố trụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>Bản mặt cầu tại chỗ C35 (dày 180mm)</t>
+        </is>
+      </c>
+      <c r="C16" s="70" t="inlineStr">
+        <is>
+          <t>Dày 180mm, L=118.2m, B=12.0m</t>
+        </is>
+      </c>
+      <c r="D16" s="71" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="F16" s="71" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G16" s="71" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H16" s="70" t="inlineStr">
+        <is>
+          <t>Phối hợp 510 tấm ván khuôn đúc sẵn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>Bản quá độ sau 2 mố &amp; đắp K98 đầu cầu</t>
+        </is>
+      </c>
+      <c r="C17" s="70" t="inlineStr">
+        <is>
+          <t>2 bản L=5.0m sau mố M1, M2</t>
+        </is>
+      </c>
+      <c r="D17" s="71" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="F17" s="71" t="n">
+        <v>86</v>
+      </c>
+      <c r="G17" s="71" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H17" s="70" t="inlineStr">
+        <is>
+          <t>Đắp chọn lọc K98 đầm chặt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>Gờ lan can bê tông &amp; khe co giãn, thảm BTN</t>
+        </is>
+      </c>
+      <c r="C18" s="70" t="inlineStr">
+        <is>
+          <t>Gờ LC 2 bên L=260.8m, BTN C16 7cm</t>
+        </is>
+      </c>
+      <c r="D18" s="71" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="F18" s="71" t="n">
+        <v>380</v>
+      </c>
+      <c r="G18" s="71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" s="70" t="inlineStr">
+        <is>
+          <t>Thảm BTN C16 diện tích 1,620 m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="72" t="n"/>
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TOÀN CÔNG TRÌNH CẦU KM19+529.080 (100%)</t>
         </is>
       </c>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="63">
-        <f>SUM(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="63">
-        <f>SUM(F4:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="66">
-        <f>SUM(G4:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="61" t="n"/>
+      <c r="C19" s="72" t="n"/>
+      <c r="D19" s="73">
+        <f>SUM(D4:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="74">
+        <f>SUM(F4:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="73">
+        <f>SUM(G4:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="72" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="75" t="n"/>
+      <c r="B20" s="75" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="75" t="n"/>
+      <c r="F20" s="75" t="n"/>
+      <c r="G20" s="75" t="n"/>
+      <c r="H20" s="75" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="75" t="n"/>
+      <c r="B21" s="75" t="n"/>
+      <c r="C21" s="75" t="n"/>
+      <c r="D21" s="75" t="n"/>
+      <c r="E21" s="75" t="n"/>
+      <c r="F21" s="75" t="n"/>
+      <c r="G21" s="75" t="n"/>
+      <c r="H21" s="75" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="75" t="n"/>
+      <c r="B22" s="75" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="75" t="n"/>
+      <c r="F22" s="75" t="n"/>
+      <c r="G22" s="75" t="n"/>
+      <c r="H22" s="75" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="75" t="n"/>
+      <c r="B23" s="75" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="75" t="n"/>
+      <c r="G23" s="75" t="n"/>
+      <c r="H23" s="75" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
